--- a/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
+++ b/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Mã tài sản (nội bộ)</t>
+          <t>Mã tài sản</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Số serial (NSX)</t>
+          <t>Số serial NSX</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Mã quản lý nội bộ duy nhất. Để trống = tự sinh.</t>
+          <t>Mã định danh nội bộ duy nhất. Chỉ chữ, số và . _ - / (không khoảng trắng, không dấu). Để trống = hệ thống tự sinh.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Số serial do nhà sản xuất cấp (Serial Number).</t>
+          <t>Số serial do nhà sản xuất cấp — KHÁC Mã tài sản. Không bắt buộc; nếu nhập phải duy nhất.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">

--- a/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
+++ b/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
@@ -563,7 +563,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Danh sách tài sản  |  Mỗi hàng = 1 tài sản. Cột đỏ bắt buộc. Các cột Link phải khớp giá trị đã có trong hệ thống hoặc file import tham chiếu.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Danh sách tài sản  |  Mỗi hàng = 1 tài sản, điền từ HÀNG 6 (hàng 5 là ví dụ mẫu). Cột đỏ bắt buộc. Danh mục / Model / Vị trí / Khoa phòng / Nhà cung cấp: điền TÊN đã có trong hệ thống (hoặc trong file tham chiếu đã nhập trước) — KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Phải khớp tên trong file 01_du_lieu_tham_chieu.xlsx / sheet 'Danh mục tài sản'.</t>
+          <t>Tên danh mục, khớp file 01 / sheet 'Danh mục tài sản'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Tên model trong file 02 / sheet 'Mô hình thiết bị'. Tự điền nếu có.</t>
+          <t>Tên model, khớp file 02 / sheet 'Mô hình thiết bị'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Tên vị trí (khớp file 01 / sheet 'Vị trí'). VD: Phòng hồi sức P301.</t>
+          <t>Tên vị trí, khớp file 01 / sheet 'Vị trí'. Điền TÊN, KHÔNG điền mã hệ thống. VD: Phòng hồi sức P301.</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Tên khoa phòng (khớp file 01 / sheet 'Khoa phòng').</t>
+          <t>Tên khoa/phòng, khớp file 01 / sheet 'Khoa phòng'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Tên NCC (khớp file 02 / sheet 'Nhà cung cấp').</t>
+          <t>Tên nhà cung cấp, khớp file 02 / sheet 'Nhà cung cấp'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Straight Line / Double Declining / Units of Production</t>
+          <t>Đường thẳng / Số dư giảm dần / Theo sản lượng / Không khấu hao.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>Draft / Commissioned / Active / Under Maintenance / Under Repair / Calibrating / Out of Service / Decommissioned</t>
+          <t>Bản nháp / Đã đưa vào sử dụng / Đang hoạt động / Đang bảo trì / Đang sửa chữa / Đang hiệu chuẩn / Ngừng hoạt động / Đã thanh lý.</t>
         </is>
       </c>
       <c r="AB4" s="6" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>Straight Line</t>
+          <t>Đường thẳng</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AA5" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Đang hoạt động</t>
         </is>
       </c>
       <c r="AB5" s="7" t="inlineStr"/>
@@ -4136,11 +4136,11 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="R5:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Straight Line,Double Declining,Units of Production"</formula1>
+    <dataValidation sqref="R6:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Đường thẳng,Số dư giảm dần,Theo sản lượng,Không khấu hao"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA5:AA105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Draft,Commissioned,Active,Under Maintenance,Under Repair,Calibrating,Out of Service,Decommissioned"</formula1>
+    <dataValidation sqref="AA6:AA105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Bản nháp,Đã đưa vào sử dụng,Đang hoạt động,Đang bảo trì,Đang sửa chữa,Đang hiệu chuẩn,Ngừng hoạt động,Đã thanh lý"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
+++ b/assetcore/public/import_templates/03_danh_sach_tai_san.xlsx
@@ -4136,10 +4136,10 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="R6:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="R6:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Đường thẳng,Số dư giảm dần,Theo sản lượng,Không khấu hao"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA6:AA105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="AA6:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Bản nháp,Đã đưa vào sử dụng,Đang hoạt động,Đang bảo trì,Đang sửa chữa,Đang hiệu chuẩn,Ngừng hoạt động,Đã thanh lý"</formula1>
     </dataValidation>
   </dataValidations>
